--- a/CATALOGO_Temas.xlsx
+++ b/CATALOGO_Temas.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -692,7 +692,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -708,7 +708,7 @@
       <c r="D6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -724,7 +724,7 @@
       <c r="D7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -740,7 +740,7 @@
       <c r="D8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -756,7 +756,7 @@
       <c r="D9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="12" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -772,7 +772,7 @@
       <c r="D10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -785,10 +785,14 @@
           <t>2425-2, 2526-1, 2526-2, 2526-3</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>En 2425-2 incluía el concepto de encapsulamiento (tema 7).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="12" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -801,10 +805,14 @@
           <t>2526-1, 2526-2, 2526-3</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>En 2425-2 se dictaba dentro del tema 6; no se registra por separado en ese trimestre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -817,10 +825,14 @@
           <t>2425-2, 2526-1, 2526-2, 2526-3</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Incluye las librerías de terceros y el consumo de APIs, que 2425-2 dictaba como sesión propia.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="12" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -836,7 +848,7 @@
       <c r="D14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -849,72 +861,36 @@
           <t>2425-2, 2526-1, 2526-2, 2526-3</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Librerías de terceros y consumo de APIs</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>2425-2</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-2; no figura en los cronogramas posteriores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Complejidad en tiempo y espacio</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>2425-2</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-2; no figura en los cronogramas posteriores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Incluye la complejidad en tiempo y espacio, que 2425-2 dictaba como sesión propia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Códigos reservados</t>
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sesión sin tema de contenido nuevo (ver tipo_sesion)</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>0</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Sesión sin tema de contenido nuevo (ver tipo_sesion)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Las sesiones de bienvenida, presentación del curso o normas de evaluación no son temas: se clasifican con tipo_sesion = administrativa. Las evaluaciones tampoco reciben código de tema; si la sesión además cubrió contenido, se le asigna el tema del cronograma y la evaluación se anota en la columna correspondiente.</t>
         </is>
@@ -989,7 +965,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1009,7 +985,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1025,7 +1001,7 @@
       <c r="D7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -1041,7 +1017,7 @@
       <c r="D8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1057,7 +1033,7 @@
       <c r="D9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="12" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -1073,7 +1049,7 @@
       <c r="D10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1089,7 +1065,7 @@
       <c r="D11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="12" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1105,7 +1081,7 @@
       <c r="D12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -1121,7 +1097,7 @@
       <c r="D13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="12" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1137,7 +1113,7 @@
       <c r="D14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1153,7 +1129,7 @@
       <c r="D15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="12" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1169,7 +1145,7 @@
       <c r="D16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -1185,7 +1161,7 @@
       <c r="D17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="12" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1240,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1271,10 +1247,11 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>El código es fijo por asignatura y se conserva entre trimestres. Los temas 1..N respetan la numeración del cronograma; los propios de un solo trimestre se agregan al final.</t>
-        </is>
-      </c>
-    </row>
+          <t>El código es fijo por asignatura y se conserva entre trimestres. Los temas se agruparon en superclases: contenidos conceptualmente relacionados comparten una misma fila, hayan sido dictados en uno o varios trimestres. La columna observación indica qué denominaciones absorbe cada superclase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -1298,545 +1275,187 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Antecedentes y definición de una red neuronal artificial</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Antecedentes, definición de una red neuronal artificial</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>2526-1, 2526-2, 2526-3</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Retropropagación</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>2425-3, 2526-1, 2526-2, 2526-3</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2425-3, 2526-1, 2526-2, 2526-3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Redes a capas</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>2425-3, 2526-1, 2526-2, 2526-3</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aplicaciones de redes neurales</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2425-3, 2526-1, 2526-2, 2526-3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Superclase (indicación del docente). Absorbe: redes a capas, redes profundas, convolucionales, recurrentes, mecanismos de atención, análisis de imágenes, análisis de texto, perceptrón y Adaline.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Redes profundas</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Agentes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>2526-3</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Redes neuronales convolucionales</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aprendizaje por refuerzo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>2425-3, 2526-3</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Redes neuronales recurrentes</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>2425-3, 2526-3</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Algoritmo genético</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2425-3, 2526-1, 2526-2, 2526-3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Superclase (indicación del docente). Absorbe: aspectos básicos de la evolución natural, componentes de un algoritmo genético simple, AGM, aplicaciones de algoritmos genéticos, codificación de la población, operadores genéticos, codificación de un AGM.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Mecanismos de atención</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>2526-3</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Preprocesamiento</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2425-3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Agentes</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>2526-3</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tipos de entrenamiento</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2425-3, 2526-1, 2526-2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Absorbe: deep reinforcement learning (2425-3), subtema según el docente.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Aprendizaje por refuerzo</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>2425-3, 2526-3</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Aspectos básicos de la evolución natural</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>2526-1, 2526-3</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Componentes de un algoritmo genético simple</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>2425-3, 2526-2, 2526-3</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr"/>
-    </row>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Autómatas</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2526-1, 2526-2, 2526-3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Superclase (indicación del docente). Absorbe: autómatas celulares, tipos de autómatas celulares, tipos de vecindades, autómatas Wolfram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Algoritmo genético modificado (AGM)</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>2425-3, 2526-1, 2526-2, 2526-3</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Códigos reservados</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Aplicaciones de algoritmos genéticos</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>2526-1, 2526-2, 2526-3</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Autómatas</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>2526-1, 2526-2, 2526-3</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr"/>
-    </row>
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sesión sin tema de contenido nuevo (ver tipo_sesion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Tipos de autómatas celulares</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>2526-1, 2526-2, 2526-3</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Tipos de vecindades</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>2526-1, 2526-2, 2526-3</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Autómatas Wolfram</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>2526-3</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Perceptrón</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Adaline</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Preprocesamiento</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Tipos de entrenamiento</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>2526-1, 2526-2</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Aplicaciones de redes neurales</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>2526-1, 2526-2</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Análisis de imágenes</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Análisis de texto</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Deep reinforcement learning</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Algoritmo genético</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>2425-3, 2526-1</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Codificación de la población</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Operadores genéticos</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Codificación de un AGM</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>2425-3</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Sólo en 2425-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Autómatas celulares</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>2526-1, 2526-2</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Códigos reservados</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>0</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Sesión sin tema de contenido nuevo (ver tipo_sesion)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Las sesiones de bienvenida, presentación del curso o normas de evaluación no son temas: se clasifican con tipo_sesion = administrativa. Las evaluaciones tampoco reciben código de tema; si la sesión además cubrió contenido, se le asigna el tema del cronograma y la evaluación se anota en la columna correspondiente.</t>
         </is>
